--- a/demo/data/students.xlsx
+++ b/demo/data/students.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\multiProgramming\demo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41DCE93-204A-4865-83BD-0FC8F33E787B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E016F6-ADCB-4F2C-9390-ADCB6961B96F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="학생정보" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>김철수</t>
   </si>
@@ -80,12 +80,28 @@
   <si>
     <t>컴퓨터공학과</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260011</t>
+  </si>
+  <si>
+    <t>김길동</t>
+  </si>
+  <si>
+    <t>최길동</t>
+  </si>
+  <si>
+    <t>20260001</t>
+  </si>
+  <si>
+    <t>20260012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -662,90 +678,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.875"/>
+    <col min="2" max="2" customWidth="true" width="17.25"/>
+    <col min="3" max="3" customWidth="true" width="13.75"/>
+    <col min="4" max="4" customWidth="true" width="16.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>20260001</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0">
+        <v>20260002</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0">
+        <v>20260003</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0">
+        <v>20260004</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s" s="0">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>20260002</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>20260003</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>20260004</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>20260005</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -756,73 +772,101 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>20260006</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>20260007</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>20260008</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>20260009</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>20260010</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -837,86 +881,86 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="16.875"/>
+    <col min="2" max="2" customWidth="true" width="14.625"/>
+    <col min="4" max="4" customWidth="true" width="22.125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>20260001</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>20260002</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>20260003</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>20260004</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>20260005</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -927,72 +971,72 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>20260006</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>20260007</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>20260008</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>20260009</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>20260010</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>2</v>
       </c>
     </row>
